--- a/data/reviews/human_reviews/human_reviews_human-y1.xlsx
+++ b/data/reviews/human_reviews/human_reviews_human-y1.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eveyhuang/Documents/NICO/ai-scientist/qualitative_evaluation/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB884F38-1069-D946-B04D-176AAC859EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="23840" yWindow="7640" windowWidth="28040" windowHeight="17440" xr2:uid="{63BAB5CA-8E1E-9346-9166-AF00D28F74E3}"/>
+    <workbookView windowWidth="20900" windowHeight="22260" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,18 +28,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="271">
   <si>
     <t>year</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>reviewer_id</t>
+  </si>
+  <si>
+    <t>scientific_merit_and_innovation_justification</t>
+  </si>
+  <si>
+    <t>scientific_merit_and_innovation_score</t>
+  </si>
+  <si>
+    <t>feasibility_justification</t>
+  </si>
+  <si>
+    <t>feasibility_score</t>
+  </si>
+  <si>
+    <t>data_sources_and_limitations_justification</t>
+  </si>
+  <si>
+    <t>data_sources_and_limitations_score</t>
+  </si>
+  <si>
+    <t>open_science_compliance_justification</t>
+  </si>
+  <si>
+    <t>open_science_compliance_score</t>
+  </si>
+  <si>
+    <t>overall_rating_summary</t>
+  </si>
+  <si>
+    <t>overall_rating_score</t>
+  </si>
+  <si>
     <t>y1</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>title</t>
   </si>
   <si>
     <t>CYTOKINETIC BOTTLENECKS OF HEAT WAVES</t>
@@ -56,36 +81,6 @@
     <t>Team leaders identify cytokinesis as a major cellular process that likely underlies emergent phenomena that differentiates heat tolerant from heat sensitive plant species. 
 The hypothesis that cytokinetic bottlenecks can be identified via interspecies data sets is novel and has the potential to reveal impactful insights into heat stress of species as well as translational applications for environmental and crop resilience. 
 The approach is highly logical and appears rigorous. The proposed methodology would benefit from expanded description, but this appears to be more a result of limited text/page limits than ill-defined methodology.</t>
-  </si>
-  <si>
-    <t>scientific_merit_and_innovation_score</t>
-  </si>
-  <si>
-    <t>scientific_merit_and_innovation_justification</t>
-  </si>
-  <si>
-    <t>feasibility_justification</t>
-  </si>
-  <si>
-    <t>feasibility_score</t>
-  </si>
-  <si>
-    <t>data_sources_and_limitations_justification</t>
-  </si>
-  <si>
-    <t>data_sources_and_limitations_score</t>
-  </si>
-  <si>
-    <t>open_science_compliance_justification</t>
-  </si>
-  <si>
-    <t>open_science_compliance_score</t>
-  </si>
-  <si>
-    <t>overall_rating_summary</t>
-  </si>
-  <si>
-    <t>overall_rating_score</t>
   </si>
   <si>
     <t>NA</t>
@@ -112,30 +107,6 @@
 Novelty &amp; Significance: 
 The proposed research is highly innovative as it aims to identify  cytokinetic bottlenecks under heat stress, which has not been  extensively studied previously. This approach could substantially  advance our understanding of plant responses to climate change,  particularly in terms of cellular and molecular adaptations. The  focus on comparing responses in heat-tolerant versus susceptible  species adds significant value to the novelty of the research. Rigor of Approach: 
 The methodology is well-articulated and robust, employing  advanced omics techniques and data integration to study  cytokinesis under heat stress. The use of publicly available single cell and whole-organ omics data ensures a comprehensive analysis.  Furthermore, the proposal outlines a clear, logical progression of  experiments designed to build on one another, enhancing the rigor  and potential success of the research outcomes.</t>
-  </si>
-  <si>
-    <t>Synthesis Focus: 
-The proposal is a textbook example of a synthesis project. It aims to  integrate multi-omics data across various plant species to elucidate  how heat waves impact cytokinesis, focusing on identifying  conserved and divergent responses. The synthesis approach is  central to the project's objectives and is clearly articulated as a means to advance understanding of emergent phenomena in plant  biology. 
-Data Identification: 
-The proposal excellently identifies specific data sources, including  both publicly available datasets and data to be generated during  the project. It references several well-established data repositories  and details the types of data (e.g., transcriptomic, proteomic) to be  used. 
-The limitations of the data, such as potential biases in public  datasets and the challenges of cross-species data integration, are  well-recognized and addressed. The proposal outlines strategies to  mitigate these limitations, such as the use of advanced  computational tools to normalize and analyze heterogeneous data  sets, enhancing the credibility of the research approach.</t>
-  </si>
-  <si>
-    <t>The proposal strongly emphasizes adherence to open  science principles, which is evident in its detailed plan for data  sharing, publication strategies, and methodologies designed to  enhance reproducibility and transparency. 
-Strengths: 
-Data Sharing: The proposal outlines a comprehensive plan to make  all collected and processed data publicly available through well recognized repositories. This ensures that data generated by the  project can be accessed by the broader scientific community,  promoting further research and validation. 
-Methodological Transparency: Detailed protocols for all  experimental and computational methods will be documented and  shared via open-access platforms. This approach not only facilitates  reproducibility but also supports other researchers in replicating  and building upon the work. 
-Collaborative Tools: The proposal includes the use of collaborative  software and platforms that support open science practices, such as  GitHub for code sharing and version control, and collaborative  writing tools for manuscript preparation, ensuring that all outputs are readily accessible and contributable by team members  
-regardless of location. 
-Weaknesses: 
-The proposal could enhance its commitment to open science by  
-incorporating plans for pre-registering research designs and  
-analysis plans, which would further boost the transparency and  
-accountability of the research process. 
-While the proposal plans for open sharing of data and  
-methodologies, it could specify timelines for data release relative to  
-project milestones or publication dates, ensuring timely access for  
-the community.</t>
   </si>
   <si>
     <t>The proposal lays out an ambitious yet structured  research plan, aiming to dissect the impacts of heat waves on  cytokinetic processes in various plant species. The outlined timeline  spans three years, divided into distinct phases focusing on data  collection, analysis, and validation. Strengths: 
@@ -157,6 +128,30 @@
 are common in studies involving extensive omics data.</t>
   </si>
   <si>
+    <t>Synthesis Focus: 
+The proposal is a textbook example of a synthesis project. It aims to  integrate multi-omics data across various plant species to elucidate  how heat waves impact cytokinesis, focusing on identifying  conserved and divergent responses. The synthesis approach is  central to the project's objectives and is clearly articulated as a means to advance understanding of emergent phenomena in plant  biology. 
+Data Identification: 
+The proposal excellently identifies specific data sources, including  both publicly available datasets and data to be generated during  the project. It references several well-established data repositories  and details the types of data (e.g., transcriptomic, proteomic) to be  used. 
+The limitations of the data, such as potential biases in public  datasets and the challenges of cross-species data integration, are  well-recognized and addressed. The proposal outlines strategies to  mitigate these limitations, such as the use of advanced  computational tools to normalize and analyze heterogeneous data  sets, enhancing the credibility of the research approach.</t>
+  </si>
+  <si>
+    <t>The proposal strongly emphasizes adherence to open  science principles, which is evident in its detailed plan for data  sharing, publication strategies, and methodologies designed to  enhance reproducibility and transparency. 
+Strengths: 
+Data Sharing: The proposal outlines a comprehensive plan to make  all collected and processed data publicly available through well recognized repositories. This ensures that data generated by the  project can be accessed by the broader scientific community,  promoting further research and validation. 
+Methodological Transparency: Detailed protocols for all  experimental and computational methods will be documented and  shared via open-access platforms. This approach not only facilitates  reproducibility but also supports other researchers in replicating  and building upon the work. 
+Collaborative Tools: The proposal includes the use of collaborative  software and platforms that support open science practices, such as  GitHub for code sharing and version control, and collaborative  writing tools for manuscript preparation, ensuring that all outputs are readily accessible and contributable by team members  
+regardless of location. 
+Weaknesses: 
+The proposal could enhance its commitment to open science by  
+incorporating plans for pre-registering research designs and  
+analysis plans, which would further boost the transparency and  
+accountability of the research process. 
+While the proposal plans for open sharing of data and  
+methodologies, it could specify timelines for data release relative to  
+project milestones or publication dates, ensuring timely access for  
+the community.</t>
+  </si>
+  <si>
     <t>he proposal submitted for the NCEMS funding is  outstanding and demonstrates a high level of sophistication,  innovation, and alignment with the goals of NCEMS. The research  focuses on emergent phenomena in plant biology under heat  stress, a timely and significant area of study given current global  climate challenges. The project stands out for its comprehensive  approach to integrating multi-species omics data to investigate the  effects of heat waves on plant cytokinesis, a critical aspect of  cellular division that remains underexplored in the context of  environmental stress. 
 Strengths: 
 Scientific Merit and Innovation: The proposal is exceptionally strong  in its scientific approach, aiming to fill a significant gap in our  understanding of plant responses to heat stress. The use of  advanced omics techniques and the focus on emergent phenomena  at the mesoscale are both highly innovative and likely to contribute  significant new insights to the field. 
@@ -211,8 +206,7 @@
 project and strongly support it</t>
   </si>
   <si>
-    <t>While the motivation for the research was a strength,  the lack of innovation in the proposed bioinformatics analysis was a  weakness--no new methodology was proposed to sort, parse, filter,  
-or integrate datasets. An outline of the sequence of steps for the  bioinformatics analysis would have been helpful.</t>
+    <t>While the motivation for the research was a strength,  the lack of innovation in the proposed bioinformatics analysis was a  weakness--no new methodology was proposed to sort, parse, filter,  or integrate datasets. An outline of the sequence of steps for the  bioinformatics analysis would have been helpful.</t>
   </si>
   <si>
     <t>The proposed project is feasible within the 2-year plan  included in the timeline.</t>
@@ -983,62 +977,456 @@
 To improve accuracy and avoid hallucinations, the proposal could benefit from iterative validation steps and feedback loops, involving multiple rounds of testing with expert input. Allocating additional buffer time for these tasks would help manage unforeseen challenges and ensure higher reliability.</t>
   </si>
   <si>
-    <t>reviewer_id</t>
+    <t>proposal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author </t>
+  </si>
+  <si>
+    <t>human review</t>
+  </si>
+  <si>
+    <t>GPT</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>human-y1</t>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; The proposed research is highly innovative as it aims to identify  cytokinetic bottlenecks under heat stress, which has not been  extensively studied previously. This approach could substantially  advance our understanding of plant responses to climate change,  particularly in terms of cellular and molecular adaptations. The  focus on comparing responses in heat-tolerant versus susceptible  species adds significant value to the novelty of the research.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; While the motivation for the research was a strength,  the lack of innovation in the proposed bioinformatics analysis was a  weakness--no new methodology was proposed to sort, parse, filter,  or integrate datasets. An outline of the sequence of steps for the  bioinformatics analysis would have been helpful.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Display"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1046,36 +1434,328 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1124,7 +1804,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1157,26 +1837,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1209,23 +1872,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1387,2141 +2033,2198 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05BF02B-5287-7141-B8AA-133FE499772C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
   <cols>
-    <col min="4" max="4" width="6.1640625" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="7.40277777777778" customWidth="1"/>
+    <col min="5" max="5" width="38.6597222222222" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.6666666666667" customWidth="1"/>
     <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="7.33333333333333" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="13" max="13" width="18.1640625" customWidth="1"/>
+    <col min="13" max="13" width="18.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" ht="409.5" spans="1:14">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
+      <c r="E2" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="409.5" spans="1:14">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>21</v>
+      <c r="E3" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>24</v>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="H3">
         <v>4</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>22</v>
+      <c r="I3" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>23</v>
+      <c r="K3" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>25</v>
+      <c r="M3" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" ht="409.5" spans="1:14">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>26</v>
+      <c r="E4" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="F4">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>27</v>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="H4">
         <v>4</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>28</v>
+      <c r="I4" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>29</v>
+      <c r="K4" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>30</v>
+      <c r="M4" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="5" ht="409.5" spans="1:14">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>31</v>
+      <c r="E5" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>33</v>
+      <c r="I5" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L5">
         <v>3</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>35</v>
+      <c r="M5" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="N5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="6" ht="409.5" spans="1:14">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>36</v>
+      <c r="C6" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>37</v>
+      <c r="E6" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:14">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
+      <c r="C7" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>42</v>
+      <c r="E7" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>44</v>
+        <v>17</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="J7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="N7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="409.5" spans="1:14">
       <c r="A8" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>36</v>
+      <c r="C8" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>47</v>
+      <c r="E8" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>49</v>
+        <v>17</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L8" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>51</v>
+        <v>17</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="N8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:14">
       <c r="A9" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>52</v>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>53</v>
+      <c r="E9" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>54</v>
+        <v>17</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>55</v>
+        <v>17</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>56</v>
+        <v>17</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="L9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>57</v>
+        <v>17</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="N9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="404" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="229" spans="1:14">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>52</v>
+      <c r="C10" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>58</v>
+      <c r="E10" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>60</v>
+        <v>17</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L10" t="s">
-        <v>16</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>62</v>
+        <v>17</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="N10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4">
         <v>3</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="4">
         <v>3</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>64</v>
       </c>
+      <c r="F11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="H11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>65</v>
+        <v>17</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L11" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>67</v>
+        <v>17</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="N11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" ht="409.5" spans="1:14">
+      <c r="A12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4">
         <v>3</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="4">
         <v>4</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>16</v>
+      <c r="E12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>70</v>
+        <v>17</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L12" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>72</v>
+        <v>17</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="N12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="409.5" spans="1:14">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>73</v>
+      <c r="C13" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>74</v>
+      <c r="E13" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>76</v>
+        <v>17</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L13" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>78</v>
+        <v>17</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="N13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="409.5" spans="1:14">
       <c r="A14" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>73</v>
+      <c r="C14" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>79</v>
+      <c r="E14" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>81</v>
+        <v>17</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L14" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>83</v>
+        <v>17</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="N14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" ht="409.5" spans="1:14">
       <c r="A15" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>73</v>
+      <c r="C15" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>84</v>
+      <c r="E15" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>86</v>
+        <v>17</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L15" t="s">
-        <v>16</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>88</v>
+        <v>17</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="N15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="409.5" spans="1:14">
       <c r="A16" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>73</v>
+      <c r="C16" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>89</v>
+      <c r="E16" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>90</v>
+        <v>17</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>91</v>
+        <v>17</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="J16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>92</v>
+        <v>17</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="L16" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>93</v>
+        <v>17</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="N16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="409.5" spans="1:14">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>5</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>94</v>
+      <c r="C17" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>95</v>
+      <c r="E17" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>97</v>
+        <v>17</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="J17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>99</v>
+        <v>17</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="N17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" ht="409.5" spans="1:14">
       <c r="A18" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>94</v>
+      <c r="C18" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>100</v>
+      <c r="E18" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>101</v>
+        <v>17</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>102</v>
+        <v>17</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>103</v>
+        <v>17</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="L18" t="s">
-        <v>16</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>104</v>
+        <v>17</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="N18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="409.5" spans="1:14">
       <c r="A19" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B19">
         <v>5</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>94</v>
+      <c r="C19" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>105</v>
+      <c r="E19" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>107</v>
+        <v>17</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="J19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L19" t="s">
-        <v>16</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>109</v>
+        <v>17</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="N19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" ht="409.5" spans="1:14">
       <c r="A20" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B20">
         <v>5</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>94</v>
+      <c r="C20" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>110</v>
+      <c r="E20" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>111</v>
+        <v>17</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>112</v>
+        <v>17</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>113</v>
+        <v>17</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="L20" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>114</v>
+        <v>17</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="N20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="409.5" spans="1:14">
       <c r="A21" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>115</v>
+      <c r="C21" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>116</v>
+      <c r="E21" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>118</v>
+        <v>17</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L21" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>120</v>
+        <v>17</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="N21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" ht="409.5" spans="1:14">
       <c r="A22" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>115</v>
+      <c r="C22" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>121</v>
+      <c r="E22" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>122</v>
+        <v>17</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>123</v>
+        <v>17</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>124</v>
+        <v>17</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="L22" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>125</v>
+        <v>17</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="N22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="409.5" spans="1:14">
       <c r="A23" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>115</v>
+      <c r="C23" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>126</v>
+      <c r="E23" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>128</v>
+        <v>17</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="J23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L23" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>130</v>
+        <v>17</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="N23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="409.5" spans="1:14">
       <c r="A24" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B24">
         <v>6</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>115</v>
+      <c r="C24" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>131</v>
+      <c r="E24" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>132</v>
+        <v>17</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>133</v>
+        <v>17</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="J24" t="s">
-        <v>16</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>134</v>
+        <v>17</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="L24" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>135</v>
+        <v>17</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="N24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" ht="409.5" spans="1:14">
       <c r="A25" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B25">
         <v>7</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>136</v>
+      <c r="C25" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>137</v>
+      <c r="E25" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="F25">
         <v>3</v>
       </c>
       <c r="G25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H25">
         <v>4</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>139</v>
+      <c r="I25" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="J25">
         <v>5</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>140</v>
+      <c r="K25" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="L25">
         <v>5</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>141</v>
+      <c r="M25" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="N25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="404" x14ac:dyDescent="0.2">
+    <row r="26" ht="405" spans="1:14">
       <c r="A26" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B26">
         <v>7</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>136</v>
+      <c r="C26" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>142</v>
+      <c r="E26" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>143</v>
+      <c r="G26" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="H26">
         <v>2</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>144</v>
+      <c r="I26" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="J26">
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L26">
         <v>3</v>
       </c>
-      <c r="M26" s="4" t="s">
-        <v>146</v>
+      <c r="M26" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="N26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="27" ht="409.5" spans="1:14">
       <c r="A27" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B27">
         <v>7</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>136</v>
+      <c r="C27" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>147</v>
+      <c r="E27" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>149</v>
+        <v>17</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L27" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>151</v>
+        <v>17</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="N27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" ht="409.5" spans="1:14">
       <c r="A28" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B28">
         <v>7</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>136</v>
+      <c r="C28" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>152</v>
+      <c r="E28" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>153</v>
+        <v>17</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>154</v>
+        <v>17</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="J28" t="s">
-        <v>16</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>155</v>
+        <v>17</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="L28" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>156</v>
+        <v>17</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="N28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" ht="409.5" spans="1:14">
       <c r="A29" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B29">
         <v>8</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>157</v>
+      <c r="C29" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>158</v>
+      <c r="E29" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>160</v>
+        <v>17</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L29" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>162</v>
+        <v>17</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="N29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" ht="409.5" spans="1:14">
       <c r="A30" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B30">
         <v>8</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>157</v>
+      <c r="C30" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>163</v>
+      <c r="E30" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>164</v>
+        <v>17</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>165</v>
+        <v>17</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>166</v>
+        <v>17</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="L30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>167</v>
+        <v>17</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="N30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" ht="409.5" spans="1:14">
       <c r="A31" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B31">
         <v>8</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>157</v>
+      <c r="C31" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>168</v>
+      <c r="E31" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>170</v>
+        <v>17</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>172</v>
+        <v>17</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="N31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" ht="409.5" spans="1:14">
       <c r="A32" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B32">
         <v>8</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>157</v>
+      <c r="C32" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>173</v>
+      <c r="E32" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>174</v>
+        <v>17</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>175</v>
+        <v>17</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>176</v>
+        <v>17</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="L32" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>177</v>
+        <v>17</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="N32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="409.5" spans="1:14">
       <c r="A33" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>157</v>
+      <c r="C33" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>178</v>
+      <c r="E33" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>180</v>
+        <v>17</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>181</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L33" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>182</v>
+        <v>17</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="N33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" ht="409.5" spans="1:14">
       <c r="A34" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B34">
         <v>9</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>183</v>
+      <c r="C34" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>184</v>
+      <c r="E34" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>185</v>
+        <v>17</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>186</v>
+        <v>17</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="J34" t="s">
-        <v>16</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>187</v>
+        <v>17</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="L34" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>188</v>
+        <v>17</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="N34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" ht="409.5" spans="1:14">
       <c r="A35" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B35">
         <v>9</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>183</v>
+      <c r="C35" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>189</v>
+      <c r="E35" s="6" t="s">
+        <v>190</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>191</v>
+        <v>17</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>192</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
-        <v>16</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>192</v>
+        <v>17</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="N35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" ht="409.5" spans="1:14">
       <c r="A36" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B36">
         <v>9</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>183</v>
+      <c r="C36" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>193</v>
+      <c r="E36" s="6" t="s">
+        <v>194</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>194</v>
+        <v>17</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>195</v>
+        <v>17</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="J36" t="s">
-        <v>16</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>196</v>
+        <v>17</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="L36" t="s">
-        <v>16</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>197</v>
+        <v>17</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>198</v>
       </c>
       <c r="N36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" ht="409.5" spans="1:14">
       <c r="A37" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B37">
         <v>10</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>198</v>
+      <c r="C37" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>199</v>
+      <c r="E37" s="6" t="s">
+        <v>200</v>
       </c>
       <c r="F37">
         <v>4.3</v>
       </c>
       <c r="G37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>201</v>
+        <v>17</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="J37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L37" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>203</v>
+        <v>17</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>204</v>
       </c>
       <c r="N37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" ht="409.5" spans="1:14">
       <c r="A38" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B38">
         <v>10</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>198</v>
+      <c r="C38" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>204</v>
+      <c r="E38" s="6" t="s">
+        <v>205</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>205</v>
+        <v>17</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>206</v>
+        <v>17</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="J38" t="s">
-        <v>16</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>207</v>
+        <v>17</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="L38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M38" s="4" t="s">
-        <v>208</v>
+        <v>17</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>209</v>
       </c>
       <c r="N38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" ht="409.5" spans="1:14">
       <c r="A39" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B39">
         <v>10</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>198</v>
+      <c r="C39" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>209</v>
+      <c r="E39" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>211</v>
+        <v>17</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="J39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L39" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" s="4" t="s">
-        <v>213</v>
+        <v>17</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="N39" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" ht="409.5" spans="1:14">
       <c r="A40" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B40">
         <v>10</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>198</v>
+      <c r="C40" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>214</v>
+      <c r="E40" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>215</v>
+        <v>17</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>216</v>
+        <v>17</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>217</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>217</v>
+        <v>17</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="L40" t="s">
-        <v>16</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>218</v>
+        <v>17</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="N40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" ht="409.5" spans="1:14">
       <c r="A41" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B41">
         <v>11</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>219</v>
+      <c r="C41" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>220</v>
+      <c r="E41" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="F41">
         <v>4</v>
       </c>
       <c r="G41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H41">
         <v>4</v>
       </c>
-      <c r="I41" s="4" t="s">
-        <v>222</v>
+      <c r="I41" s="6" t="s">
+        <v>223</v>
       </c>
       <c r="J41">
         <v>3</v>
       </c>
       <c r="K41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L41">
         <v>5</v>
       </c>
-      <c r="M41" s="4" t="s">
-        <v>224</v>
+      <c r="M41" s="6" t="s">
+        <v>225</v>
       </c>
       <c r="N41">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="42" ht="409.5" spans="1:14">
       <c r="A42" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B42">
         <v>11</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>219</v>
+      <c r="C42" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="D42">
         <v>2</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>225</v>
+      <c r="E42" s="6" t="s">
+        <v>226</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>226</v>
+        <v>17</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>227</v>
+        <v>17</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="J42" t="s">
-        <v>16</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>228</v>
+        <v>17</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="L42" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" s="4" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>230</v>
       </c>
       <c r="N42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" ht="409.5" spans="1:14">
       <c r="A43" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B43">
         <v>11</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>219</v>
+      <c r="C43" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>230</v>
+      <c r="E43" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>232</v>
+        <v>17</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>233</v>
       </c>
       <c r="J43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L43" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>234</v>
+        <v>17</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="N43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" ht="409.5" spans="1:14">
       <c r="A44" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B44">
         <v>11</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>219</v>
+      <c r="C44" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>235</v>
+      <c r="E44" s="6" t="s">
+        <v>236</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>236</v>
+        <v>17</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>237</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>237</v>
+        <v>17</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="J44" t="s">
-        <v>16</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>238</v>
+        <v>17</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>239</v>
       </c>
       <c r="L44" t="s">
-        <v>16</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>239</v>
+        <v>17</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="N44" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="340" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" ht="335" spans="1:14">
       <c r="A45" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B45">
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>241</v>
+      <c r="E45" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>243</v>
+        <v>17</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>244</v>
       </c>
       <c r="J45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L45" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>245</v>
+        <v>17</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="N45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" ht="409.5" spans="1:14">
       <c r="A46" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B46">
         <v>12</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>240</v>
+      <c r="C46" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>246</v>
+      <c r="E46" s="6" t="s">
+        <v>247</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>247</v>
+        <v>17</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>248</v>
+        <v>17</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>249</v>
       </c>
       <c r="J46" t="s">
-        <v>16</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>249</v>
+        <v>17</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>250</v>
       </c>
       <c r="L46" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" s="4" t="s">
-        <v>250</v>
+        <v>17</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="N46" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" ht="409.5" spans="1:14">
       <c r="A47" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B47">
         <v>12</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>240</v>
+      <c r="C47" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>251</v>
+      <c r="E47" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>253</v>
+        <v>17</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="J47" t="s">
-        <v>16</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>254</v>
+        <v>17</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="L47" t="s">
-        <v>16</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>255</v>
+        <v>17</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="N47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" ht="409.5" spans="1:14">
       <c r="A48" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B48">
         <v>12</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>240</v>
+      <c r="C48" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="D48">
         <v>4</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>256</v>
+      <c r="E48" s="6" t="s">
+        <v>257</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>257</v>
+        <v>17</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>258</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>258</v>
+        <v>17</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="J48" t="s">
-        <v>16</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>259</v>
+        <v>17</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="L48" t="s">
-        <v>16</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>260</v>
+        <v>17</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="N48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="17.6" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="2" width="8.88888888888889" style="1"/>
+    <col min="3" max="3" width="44.5555555555556" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5416666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.2638888888889" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88888888888889" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2" ht="159" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" ht="106" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/data/reviews/human_reviews/human_reviews_human-y1.xlsx
+++ b/data/reviews/human_reviews/human_reviews_human-y1.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20900" windowHeight="22260" activeTab="1"/>
+    <workbookView windowHeight="16020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="262">
   <si>
     <t>year</t>
   </si>
@@ -976,57 +975,6 @@
     <t>The proposal addresses the critical challenge of metadata completeness and consistency in proteomics data, essential for understanding cellular mechanisms and disease processes. Integrating bioinformatics, NLP, and LLMs for automated metadata extraction is an innovative approach that promises to enhance metadata quality and usability.
 To improve accuracy and avoid hallucinations, the proposal could benefit from iterative validation steps and feedback loops, involving multiple rounds of testing with expert input. Allocating additional buffer time for these tasks would help manage unforeseen challenges and ensure higher reliability.</t>
   </si>
-  <si>
-    <t>proposal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">author </t>
-  </si>
-  <si>
-    <t>human review</t>
-  </si>
-  <si>
-    <t>GPT</t>
-  </si>
-  <si>
-    <t>Claude</t>
-  </si>
-  <si>
-    <t>Gemini</t>
-  </si>
-  <si>
-    <t>human-y1</t>
-  </si>
-  <si>
-    <r>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>; The proposed research is highly innovative as it aims to identify  cytokinetic bottlenecks under heat stress, which has not been  extensively studied previously. This approach could substantially  advance our understanding of plant responses to climate change,  particularly in terms of cellular and molecular adaptations. The  focus on comparing responses in heat-tolerant versus susceptible  species adds significant value to the novelty of the research.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>; While the motivation for the research was a strength,  the lack of innovation in the proposed bioinformatics analysis was a  weakness--no new methodology was proposed to sort, parse, filter,  or integrate datasets. An outline of the sequence of steps for the  bioinformatics analysis would have been helpful.</t>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -1038,18 +986,10 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1535,170 +1475,164 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1708,7 +1642,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -2065,7 +1999,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -2077,7 +2011,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2103,13 +2037,13 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
@@ -2121,7 +2055,7 @@
       <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J2" t="s">
@@ -2133,7 +2067,7 @@
       <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="N2" t="s">
@@ -2147,37 +2081,37 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H3">
         <v>4</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>26</v>
       </c>
       <c r="N3">
@@ -2191,37 +2125,37 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F4">
         <v>4</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H4">
         <v>4</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="L4">
         <v>3</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N4">
@@ -2235,13 +2169,13 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="F5">
@@ -2253,7 +2187,7 @@
       <c r="H5">
         <v>5</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="J5">
@@ -2265,27 +2199,27 @@
       <c r="L5">
         <v>3</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="4" t="s">
         <v>36</v>
       </c>
       <c r="N5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="409.5" spans="1:14">
+    <row r="6" ht="247" spans="1:14">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F6" t="s">
@@ -2297,7 +2231,7 @@
       <c r="H6" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="J6" t="s">
@@ -2309,7 +2243,7 @@
       <c r="L6" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="4" t="s">
         <v>42</v>
       </c>
       <c r="N6" t="s">
@@ -2323,13 +2257,13 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F7" t="s">
@@ -2341,7 +2275,7 @@
       <c r="H7" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="4" t="s">
         <v>45</v>
       </c>
       <c r="J7" t="s">
@@ -2353,7 +2287,7 @@
       <c r="L7" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="4" t="s">
         <v>47</v>
       </c>
       <c r="N7" t="s">
@@ -2367,25 +2301,25 @@
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>49</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="4" t="s">
         <v>50</v>
       </c>
       <c r="J8" t="s">
@@ -2397,7 +2331,7 @@
       <c r="L8" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="4" t="s">
         <v>52</v>
       </c>
       <c r="N8" t="s">
@@ -2411,37 +2345,37 @@
       <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>54</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>55</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="4" t="s">
         <v>57</v>
       </c>
       <c r="L9" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="4" t="s">
         <v>58</v>
       </c>
       <c r="N9" t="s">
@@ -2455,13 +2389,13 @@
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>59</v>
       </c>
       <c r="F10" t="s">
@@ -2473,7 +2407,7 @@
       <c r="H10" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="4" t="s">
         <v>61</v>
       </c>
       <c r="J10" t="s">
@@ -2485,7 +2419,7 @@
       <c r="L10" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="4" t="s">
         <v>63</v>
       </c>
       <c r="N10" t="s">
@@ -2493,31 +2427,31 @@
       </c>
     </row>
     <row r="11" ht="409.5" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>3</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="4" t="s">
         <v>66</v>
       </c>
       <c r="J11" t="s">
@@ -2529,7 +2463,7 @@
       <c r="L11" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="4" t="s">
         <v>68</v>
       </c>
       <c r="N11" t="s">
@@ -2537,22 +2471,22 @@
       </c>
     </row>
     <row r="12" ht="409.5" spans="1:14">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
         <v>3</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>4</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
@@ -2561,7 +2495,7 @@
       <c r="H12" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="4" t="s">
         <v>71</v>
       </c>
       <c r="J12" t="s">
@@ -2573,7 +2507,7 @@
       <c r="L12" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="4" t="s">
         <v>73</v>
       </c>
       <c r="N12" t="s">
@@ -2587,13 +2521,13 @@
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>75</v>
       </c>
       <c r="F13" t="s">
@@ -2605,7 +2539,7 @@
       <c r="H13" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="4" t="s">
         <v>77</v>
       </c>
       <c r="J13" t="s">
@@ -2617,7 +2551,7 @@
       <c r="L13" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="4" t="s">
         <v>79</v>
       </c>
       <c r="N13" t="s">
@@ -2631,13 +2565,13 @@
       <c r="B14">
         <v>4</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F14" t="s">
@@ -2649,7 +2583,7 @@
       <c r="H14" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="4" t="s">
         <v>82</v>
       </c>
       <c r="J14" t="s">
@@ -2661,7 +2595,7 @@
       <c r="L14" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="4" t="s">
         <v>84</v>
       </c>
       <c r="N14" t="s">
@@ -2675,13 +2609,13 @@
       <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>85</v>
       </c>
       <c r="F15" t="s">
@@ -2693,7 +2627,7 @@
       <c r="H15" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="4" t="s">
         <v>87</v>
       </c>
       <c r="J15" t="s">
@@ -2705,7 +2639,7 @@
       <c r="L15" t="s">
         <v>17</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="4" t="s">
         <v>89</v>
       </c>
       <c r="N15" t="s">
@@ -2719,37 +2653,37 @@
       <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>90</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>91</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="4" t="s">
         <v>92</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="4" t="s">
         <v>93</v>
       </c>
       <c r="L16" t="s">
         <v>17</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="4" t="s">
         <v>94</v>
       </c>
       <c r="N16" t="s">
@@ -2763,13 +2697,13 @@
       <c r="B17">
         <v>5</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="4" t="s">
         <v>96</v>
       </c>
       <c r="F17" t="s">
@@ -2781,7 +2715,7 @@
       <c r="H17" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="4" t="s">
         <v>98</v>
       </c>
       <c r="J17" t="s">
@@ -2793,7 +2727,7 @@
       <c r="L17" t="s">
         <v>17</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="4" t="s">
         <v>100</v>
       </c>
       <c r="N17" t="s">
@@ -2807,37 +2741,37 @@
       <c r="B18">
         <v>5</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="4" t="s">
         <v>101</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="4" t="s">
         <v>103</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="4" t="s">
         <v>104</v>
       </c>
       <c r="L18" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="4" t="s">
         <v>105</v>
       </c>
       <c r="N18" t="s">
@@ -2851,13 +2785,13 @@
       <c r="B19">
         <v>5</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="4" t="s">
         <v>106</v>
       </c>
       <c r="F19" t="s">
@@ -2869,7 +2803,7 @@
       <c r="H19" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="4" t="s">
         <v>108</v>
       </c>
       <c r="J19" t="s">
@@ -2881,7 +2815,7 @@
       <c r="L19" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="M19" s="4" t="s">
         <v>110</v>
       </c>
       <c r="N19" t="s">
@@ -2895,37 +2829,37 @@
       <c r="B20">
         <v>5</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="4" t="s">
         <v>111</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="4" t="s">
         <v>112</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="4" t="s">
         <v>113</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="4" t="s">
         <v>114</v>
       </c>
       <c r="L20" t="s">
         <v>17</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="M20" s="4" t="s">
         <v>115</v>
       </c>
       <c r="N20" t="s">
@@ -2939,13 +2873,13 @@
       <c r="B21">
         <v>6</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>117</v>
       </c>
       <c r="F21" t="s">
@@ -2957,7 +2891,7 @@
       <c r="H21" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="4" t="s">
         <v>119</v>
       </c>
       <c r="J21" t="s">
@@ -2969,7 +2903,7 @@
       <c r="L21" t="s">
         <v>17</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="4" t="s">
         <v>121</v>
       </c>
       <c r="N21" t="s">
@@ -2983,37 +2917,37 @@
       <c r="B22">
         <v>6</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="4" t="s">
         <v>122</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="4" t="s">
         <v>123</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="4" t="s">
         <v>124</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="3" t="s">
         <v>125</v>
       </c>
       <c r="L22" t="s">
         <v>17</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="4" t="s">
         <v>126</v>
       </c>
       <c r="N22" t="s">
@@ -3027,13 +2961,13 @@
       <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="4" t="s">
         <v>127</v>
       </c>
       <c r="F23" t="s">
@@ -3045,7 +2979,7 @@
       <c r="H23" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="4" t="s">
         <v>129</v>
       </c>
       <c r="J23" t="s">
@@ -3057,7 +2991,7 @@
       <c r="L23" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="4" t="s">
         <v>131</v>
       </c>
       <c r="N23" t="s">
@@ -3071,37 +3005,37 @@
       <c r="B24">
         <v>6</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="4" t="s">
         <v>132</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="4" t="s">
         <v>133</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="4" t="s">
         <v>134</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="4" t="s">
         <v>135</v>
       </c>
       <c r="L24" t="s">
         <v>17</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="M24" s="4" t="s">
         <v>136</v>
       </c>
       <c r="N24" t="s">
@@ -3115,13 +3049,13 @@
       <c r="B25">
         <v>7</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F25">
@@ -3133,19 +3067,19 @@
       <c r="H25">
         <v>4</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="4" t="s">
         <v>140</v>
       </c>
       <c r="J25">
         <v>5</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K25" s="3" t="s">
         <v>141</v>
       </c>
       <c r="L25">
         <v>5</v>
       </c>
-      <c r="M25" s="6" t="s">
+      <c r="M25" s="4" t="s">
         <v>142</v>
       </c>
       <c r="N25">
@@ -3159,25 +3093,25 @@
       <c r="B26">
         <v>7</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="4" t="s">
         <v>143</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="4" t="s">
         <v>144</v>
       </c>
       <c r="H26">
         <v>2</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="4" t="s">
         <v>145</v>
       </c>
       <c r="J26">
@@ -3189,7 +3123,7 @@
       <c r="L26">
         <v>3</v>
       </c>
-      <c r="M26" s="6" t="s">
+      <c r="M26" s="4" t="s">
         <v>147</v>
       </c>
       <c r="N26">
@@ -3203,13 +3137,13 @@
       <c r="B27">
         <v>7</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="4" t="s">
         <v>148</v>
       </c>
       <c r="F27" t="s">
@@ -3221,7 +3155,7 @@
       <c r="H27" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="4" t="s">
         <v>150</v>
       </c>
       <c r="J27" t="s">
@@ -3233,7 +3167,7 @@
       <c r="L27" t="s">
         <v>17</v>
       </c>
-      <c r="M27" s="6" t="s">
+      <c r="M27" s="4" t="s">
         <v>152</v>
       </c>
       <c r="N27" t="s">
@@ -3247,37 +3181,37 @@
       <c r="B28">
         <v>7</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F28" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="4" t="s">
         <v>154</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="4" t="s">
         <v>155</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="4" t="s">
         <v>156</v>
       </c>
       <c r="L28" t="s">
         <v>17</v>
       </c>
-      <c r="M28" s="6" t="s">
+      <c r="M28" s="4" t="s">
         <v>157</v>
       </c>
       <c r="N28" t="s">
@@ -3291,13 +3225,13 @@
       <c r="B29">
         <v>8</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="4" t="s">
         <v>159</v>
       </c>
       <c r="F29" t="s">
@@ -3309,7 +3243,7 @@
       <c r="H29" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J29" t="s">
@@ -3321,7 +3255,7 @@
       <c r="L29" t="s">
         <v>17</v>
       </c>
-      <c r="M29" s="6" t="s">
+      <c r="M29" s="4" t="s">
         <v>163</v>
       </c>
       <c r="N29" t="s">
@@ -3335,37 +3269,37 @@
       <c r="B30">
         <v>8</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="4" t="s">
         <v>164</v>
       </c>
       <c r="F30" t="s">
         <v>17</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="4" t="s">
         <v>165</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="4" t="s">
         <v>166</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="4" t="s">
         <v>167</v>
       </c>
       <c r="L30" t="s">
         <v>17</v>
       </c>
-      <c r="M30" s="6" t="s">
+      <c r="M30" s="4" t="s">
         <v>168</v>
       </c>
       <c r="N30" t="s">
@@ -3379,13 +3313,13 @@
       <c r="B31">
         <v>8</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="4" t="s">
         <v>169</v>
       </c>
       <c r="F31" t="s">
@@ -3397,7 +3331,7 @@
       <c r="H31" t="s">
         <v>17</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="4" t="s">
         <v>171</v>
       </c>
       <c r="J31" t="s">
@@ -3409,7 +3343,7 @@
       <c r="L31" t="s">
         <v>17</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="M31" s="4" t="s">
         <v>173</v>
       </c>
       <c r="N31" t="s">
@@ -3423,37 +3357,37 @@
       <c r="B32">
         <v>8</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="4" t="s">
         <v>174</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="4" t="s">
         <v>175</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="4" t="s">
         <v>176</v>
       </c>
       <c r="J32" t="s">
         <v>17</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K32" s="4" t="s">
         <v>177</v>
       </c>
       <c r="L32" t="s">
         <v>17</v>
       </c>
-      <c r="M32" s="6" t="s">
+      <c r="M32" s="4" t="s">
         <v>178</v>
       </c>
       <c r="N32" t="s">
@@ -3467,13 +3401,13 @@
       <c r="B33">
         <v>8</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="4" t="s">
         <v>179</v>
       </c>
       <c r="F33" t="s">
@@ -3485,7 +3419,7 @@
       <c r="H33" t="s">
         <v>17</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="4" t="s">
         <v>181</v>
       </c>
       <c r="J33" t="s">
@@ -3497,71 +3431,71 @@
       <c r="L33" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="M33" s="4" t="s">
         <v>183</v>
       </c>
       <c r="N33" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" ht="409.5" spans="1:14">
+    <row r="34" ht="247" spans="1:14">
       <c r="A34" t="s">
         <v>14</v>
       </c>
       <c r="B34">
         <v>9</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="1" t="s">
         <v>184</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F34" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="4" t="s">
         <v>186</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="4" t="s">
         <v>187</v>
       </c>
       <c r="J34" t="s">
         <v>17</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="4" t="s">
         <v>188</v>
       </c>
       <c r="L34" t="s">
         <v>17</v>
       </c>
-      <c r="M34" s="6" t="s">
+      <c r="M34" s="4" t="s">
         <v>189</v>
       </c>
       <c r="N34" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" ht="409.5" spans="1:14">
+    <row r="35" ht="370" spans="1:14">
       <c r="A35" t="s">
         <v>14</v>
       </c>
       <c r="B35">
         <v>9</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="1" t="s">
         <v>184</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="4" t="s">
         <v>190</v>
       </c>
       <c r="F35" t="s">
@@ -3573,7 +3507,7 @@
       <c r="H35" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="4" t="s">
         <v>192</v>
       </c>
       <c r="J35" t="s">
@@ -3582,7 +3516,7 @@
       <c r="L35" t="s">
         <v>17</v>
       </c>
-      <c r="M35" s="6" t="s">
+      <c r="M35" s="4" t="s">
         <v>193</v>
       </c>
       <c r="N35" t="s">
@@ -3596,37 +3530,37 @@
       <c r="B36">
         <v>9</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="1" t="s">
         <v>184</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="4" t="s">
         <v>194</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="4" t="s">
         <v>195</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I36" s="4" t="s">
         <v>196</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="4" t="s">
         <v>197</v>
       </c>
       <c r="L36" t="s">
         <v>17</v>
       </c>
-      <c r="M36" s="6" t="s">
+      <c r="M36" s="4" t="s">
         <v>198</v>
       </c>
       <c r="N36" t="s">
@@ -3640,13 +3574,13 @@
       <c r="B37">
         <v>10</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="4" t="s">
         <v>200</v>
       </c>
       <c r="F37">
@@ -3658,7 +3592,7 @@
       <c r="H37" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="4" t="s">
         <v>202</v>
       </c>
       <c r="J37" t="s">
@@ -3670,7 +3604,7 @@
       <c r="L37" t="s">
         <v>17</v>
       </c>
-      <c r="M37" s="6" t="s">
+      <c r="M37" s="4" t="s">
         <v>204</v>
       </c>
       <c r="N37" t="s">
@@ -3684,37 +3618,37 @@
       <c r="B38">
         <v>10</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="4" t="s">
         <v>205</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="4" t="s">
         <v>206</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I38" s="4" t="s">
         <v>207</v>
       </c>
       <c r="J38" t="s">
         <v>17</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="4" t="s">
         <v>208</v>
       </c>
       <c r="L38" t="s">
         <v>17</v>
       </c>
-      <c r="M38" s="6" t="s">
+      <c r="M38" s="4" t="s">
         <v>209</v>
       </c>
       <c r="N38" t="s">
@@ -3728,13 +3662,13 @@
       <c r="B39">
         <v>10</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="4" t="s">
         <v>210</v>
       </c>
       <c r="F39" t="s">
@@ -3746,7 +3680,7 @@
       <c r="H39" t="s">
         <v>17</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="4" t="s">
         <v>212</v>
       </c>
       <c r="J39" t="s">
@@ -3758,7 +3692,7 @@
       <c r="L39" t="s">
         <v>17</v>
       </c>
-      <c r="M39" s="6" t="s">
+      <c r="M39" s="4" t="s">
         <v>214</v>
       </c>
       <c r="N39" t="s">
@@ -3772,37 +3706,37 @@
       <c r="B40">
         <v>10</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="1" t="s">
         <v>199</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="4" t="s">
         <v>215</v>
       </c>
       <c r="F40" t="s">
         <v>17</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="4" t="s">
         <v>216</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="4" t="s">
         <v>217</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="4" t="s">
         <v>218</v>
       </c>
       <c r="L40" t="s">
         <v>17</v>
       </c>
-      <c r="M40" s="6" t="s">
+      <c r="M40" s="4" t="s">
         <v>219</v>
       </c>
       <c r="N40" t="s">
@@ -3816,13 +3750,13 @@
       <c r="B41">
         <v>11</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="4" t="s">
         <v>221</v>
       </c>
       <c r="F41">
@@ -3834,7 +3768,7 @@
       <c r="H41">
         <v>4</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="4" t="s">
         <v>223</v>
       </c>
       <c r="J41">
@@ -3846,7 +3780,7 @@
       <c r="L41">
         <v>5</v>
       </c>
-      <c r="M41" s="6" t="s">
+      <c r="M41" s="4" t="s">
         <v>225</v>
       </c>
       <c r="N41">
@@ -3860,37 +3794,37 @@
       <c r="B42">
         <v>11</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D42">
         <v>2</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="4" t="s">
         <v>226</v>
       </c>
       <c r="F42" t="s">
         <v>17</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="4" t="s">
         <v>227</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="4" t="s">
         <v>228</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
       </c>
-      <c r="K42" s="6" t="s">
+      <c r="K42" s="4" t="s">
         <v>229</v>
       </c>
       <c r="L42" t="s">
         <v>17</v>
       </c>
-      <c r="M42" s="6" t="s">
+      <c r="M42" s="4" t="s">
         <v>230</v>
       </c>
       <c r="N42" t="s">
@@ -3904,13 +3838,13 @@
       <c r="B43">
         <v>11</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="4" t="s">
         <v>231</v>
       </c>
       <c r="F43" t="s">
@@ -3922,7 +3856,7 @@
       <c r="H43" t="s">
         <v>17</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="4" t="s">
         <v>233</v>
       </c>
       <c r="J43" t="s">
@@ -3934,7 +3868,7 @@
       <c r="L43" t="s">
         <v>17</v>
       </c>
-      <c r="M43" s="6" t="s">
+      <c r="M43" s="4" t="s">
         <v>235</v>
       </c>
       <c r="N43" t="s">
@@ -3948,44 +3882,44 @@
       <c r="B44">
         <v>11</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="1" t="s">
         <v>220</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="4" t="s">
         <v>236</v>
       </c>
       <c r="F44" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="4" t="s">
         <v>237</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" s="4" t="s">
         <v>238</v>
       </c>
       <c r="J44" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="4" t="s">
         <v>239</v>
       </c>
       <c r="L44" t="s">
         <v>17</v>
       </c>
-      <c r="M44" s="6" t="s">
+      <c r="M44" s="4" t="s">
         <v>240</v>
       </c>
       <c r="N44" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" ht="335" spans="1:14">
+    <row r="45" ht="300" spans="1:14">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -3998,7 +3932,7 @@
       <c r="D45">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="4" t="s">
         <v>242</v>
       </c>
       <c r="F45" t="s">
@@ -4010,7 +3944,7 @@
       <c r="H45" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="I45" s="4" t="s">
         <v>244</v>
       </c>
       <c r="J45" t="s">
@@ -4022,7 +3956,7 @@
       <c r="L45" t="s">
         <v>17</v>
       </c>
-      <c r="M45" s="6" t="s">
+      <c r="M45" s="4" t="s">
         <v>246</v>
       </c>
       <c r="N45" t="s">
@@ -4036,37 +3970,37 @@
       <c r="B46">
         <v>12</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="4" t="s">
         <v>247</v>
       </c>
       <c r="F46" t="s">
         <v>17</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="4" t="s">
         <v>248</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" s="4" t="s">
         <v>249</v>
       </c>
       <c r="J46" t="s">
         <v>17</v>
       </c>
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="4" t="s">
         <v>250</v>
       </c>
       <c r="L46" t="s">
         <v>17</v>
       </c>
-      <c r="M46" s="6" t="s">
+      <c r="M46" s="4" t="s">
         <v>251</v>
       </c>
       <c r="N46" t="s">
@@ -4080,13 +4014,13 @@
       <c r="B47">
         <v>12</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="4" t="s">
         <v>252</v>
       </c>
       <c r="F47" t="s">
@@ -4098,19 +4032,19 @@
       <c r="H47" t="s">
         <v>17</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" s="4" t="s">
         <v>254</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
       </c>
-      <c r="K47" s="6" t="s">
+      <c r="K47" s="4" t="s">
         <v>255</v>
       </c>
       <c r="L47" t="s">
         <v>17</v>
       </c>
-      <c r="M47" s="6" t="s">
+      <c r="M47" s="4" t="s">
         <v>256</v>
       </c>
       <c r="N47" t="s">
@@ -4124,37 +4058,37 @@
       <c r="B48">
         <v>12</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="1" t="s">
         <v>241</v>
       </c>
       <c r="D48">
         <v>4</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="4" t="s">
         <v>257</v>
       </c>
       <c r="F48" t="s">
         <v>17</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="4" t="s">
         <v>258</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="I48" s="4" t="s">
         <v>259</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="K48" s="4" t="s">
         <v>260</v>
       </c>
       <c r="L48" t="s">
         <v>17</v>
       </c>
-      <c r="M48" s="6" t="s">
+      <c r="M48" s="4" t="s">
         <v>261</v>
       </c>
       <c r="N48" t="s">
@@ -4165,66 +4099,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="17.6" outlineLevelRow="2" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="2" width="8.88888888888889" style="1"/>
-    <col min="3" max="3" width="44.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.5416666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.2638888888889" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88888888888889" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="2" ht="159" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="3" ht="106" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>